--- a/results/02_taxa_assemblage/LDA_Method/ModelA_CoreOnly/tables/site_eval_train.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelA_CoreOnly/tables/site_eval_train.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,20 +461,15 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Prob_Cluster 3</t>
+          <t>p_max</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>p_max</t>
+          <t>delta_p</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>delta_p</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
@@ -487,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -498,21 +493,18 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.383561707846182</v>
+        <v>0.7689153019604682</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3013524728324307</v>
+        <v>0.2310846980395318</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3150858193213872</v>
+        <v>0.7689153019604682</v>
       </c>
       <c r="H2" t="n">
-        <v>0.383561707846182</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.0684758885247948</v>
-      </c>
-      <c r="J2" t="inlineStr">
+        <v>0.5378306039209364</v>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -533,24 +525,21 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1380990955562912</v>
+        <v>0.9892060918429344</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2680402419844067</v>
+        <v>0.01079390815706563</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5938606624593021</v>
+        <v>0.9892060918429344</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5938606624593021</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.3258204204748954</v>
-      </c>
-      <c r="J3" t="inlineStr">
+        <v>0.9784121836858688</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -559,11 +548,11 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>011A</t>
+          <t>030ABC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -571,24 +560,21 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1017330223870971</v>
+        <v>0.005476933588521415</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4266153222315044</v>
+        <v>0.9945230664114786</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4716516553813985</v>
+        <v>0.9945230664114786</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4716516553813985</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.04503633314989408</v>
-      </c>
-      <c r="J4" t="inlineStr">
+        <v>0.9890461328229572</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -597,7 +583,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>035C</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -612,21 +598,18 @@
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0638260054384322</v>
+        <v>0.006780117977516764</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7707883808742433</v>
+        <v>0.9932198820224832</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1653856136873246</v>
+        <v>0.9932198820224832</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7707883808742433</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.6054027671869187</v>
-      </c>
-      <c r="J5" t="inlineStr">
+        <v>0.9864397640449665</v>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -635,11 +618,11 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>036C</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -650,21 +633,18 @@
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04582460238599239</v>
+        <v>0.4422701231135817</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8776871067162679</v>
+        <v>0.5577298768864183</v>
       </c>
       <c r="G6" t="n">
-        <v>0.07648829089773955</v>
+        <v>0.5577298768864183</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8776871067162679</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.8011988158185284</v>
-      </c>
-      <c r="J6" t="inlineStr">
+        <v>0.1154597537728366</v>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -673,7 +653,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>058C</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -688,21 +668,18 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01415555820499548</v>
+        <v>0.2339450307099349</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9203214738824143</v>
+        <v>0.7660549692900651</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06552296791259021</v>
+        <v>0.7660549692900651</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9203214738824143</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.854798505969824</v>
-      </c>
-      <c r="J7" t="inlineStr">
+        <v>0.5321099385801302</v>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -711,11 +688,11 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>060B</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -726,21 +703,18 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0756780991503775</v>
+        <v>0.08215339293955648</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7417948167838142</v>
+        <v>0.9178466070604435</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1825270840658083</v>
+        <v>0.9178466070604435</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7417948167838142</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.5592677327180059</v>
-      </c>
-      <c r="J8" t="inlineStr">
+        <v>0.835693214120887</v>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -749,11 +723,11 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>068B</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -761,24 +735,21 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1866388515939265</v>
+        <v>0.7847257475103423</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6170806312259357</v>
+        <v>0.2152742524896577</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1962805171801377</v>
+        <v>0.7847257475103423</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6170806312259357</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.420800114045798</v>
-      </c>
-      <c r="J9" t="inlineStr">
+        <v>0.5694514950206846</v>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -787,7 +758,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>071B</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -802,21 +773,18 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1314321725659108</v>
+        <v>0.003312082133667404</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7374868241987926</v>
+        <v>0.9966879178663326</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1310810032352966</v>
+        <v>0.9966879178663326</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7374868241987926</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.6060546516328819</v>
-      </c>
-      <c r="J10" t="inlineStr">
+        <v>0.9933758357326652</v>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -825,11 +793,11 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>094C</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -837,24 +805,21 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0673552027781438</v>
+        <v>0.007356279957328904</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02183022394618297</v>
+        <v>0.9926437200426711</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9108145732756732</v>
+        <v>0.9926437200426711</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9108145732756732</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.8434593704975294</v>
-      </c>
-      <c r="J11" t="inlineStr">
+        <v>0.9852874400853422</v>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -863,11 +828,11 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>125A</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -875,24 +840,21 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1006483137550782</v>
+        <v>0.1225351454942969</v>
       </c>
       <c r="F12" t="n">
-        <v>0.05914648781582437</v>
+        <v>0.8774648545057031</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8402051984290976</v>
+        <v>0.8774648545057031</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8402051984290976</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.7395568846740194</v>
-      </c>
-      <c r="J12" t="inlineStr">
+        <v>0.7549297090114062</v>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -901,11 +863,11 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -913,24 +875,21 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1044009424865093</v>
+        <v>0.8176438681423801</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4454157684649215</v>
+        <v>0.1823561318576199</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4501832890485693</v>
+        <v>0.8176438681423801</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4501832890485693</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.004767520583647822</v>
-      </c>
-      <c r="J13" t="inlineStr">
+        <v>0.6352877362847602</v>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -939,11 +898,11 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -951,24 +910,21 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01883836106928195</v>
+        <v>0.9953789411656835</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8789413201009331</v>
+        <v>0.004621058834316526</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1022203188297851</v>
+        <v>0.9953789411656835</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8789413201009331</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.776721001271148</v>
-      </c>
-      <c r="J14" t="inlineStr">
+        <v>0.990757882331367</v>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -977,7 +933,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -989,24 +945,21 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0.06019839708591188</v>
+        <v>0.9928575214681447</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6977227042449797</v>
+        <v>0.007142478531855361</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2420788986691086</v>
+        <v>0.9928575214681447</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6977227042449797</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.4556438055758711</v>
-      </c>
-      <c r="J15" t="inlineStr">
+        <v>0.9857150429362893</v>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1015,11 +968,11 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,24 +980,21 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2431761297472401</v>
+        <v>0.9984305728276426</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4722087261815572</v>
+        <v>0.001569427172357375</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2846151440712026</v>
+        <v>0.9984305728276426</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4722087261815572</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.1875935821103546</v>
-      </c>
-      <c r="J16" t="inlineStr">
+        <v>0.9968611456552852</v>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1053,11 +1003,11 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1065,24 +1015,21 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1539713331982049</v>
+        <v>0.9927843502988174</v>
       </c>
       <c r="F17" t="n">
-        <v>0.656300315903292</v>
+        <v>0.007215649701182634</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1897283508985031</v>
+        <v>0.9927843502988174</v>
       </c>
       <c r="H17" t="n">
-        <v>0.656300315903292</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.4665719650047888</v>
-      </c>
-      <c r="J17" t="inlineStr">
+        <v>0.9855687005976348</v>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1091,7 +1038,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1103,24 +1050,21 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>0.211267962287696</v>
+        <v>0.9988961462969597</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1297735069402902</v>
+        <v>0.001103853703040309</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6589585307720138</v>
+        <v>0.9988961462969597</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6589585307720138</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.4476905684843179</v>
-      </c>
-      <c r="J18" t="inlineStr">
+        <v>0.9977922925939193</v>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1129,11 +1073,11 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>S37</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1141,24 +1085,21 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0.07202114962652548</v>
+        <v>0.9979900585009416</v>
       </c>
       <c r="F19" t="n">
-        <v>0.08244560639673301</v>
+        <v>0.002009941499058425</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8455332439767416</v>
+        <v>0.9979900585009416</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8455332439767416</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.7630876375800085</v>
-      </c>
-      <c r="J19" t="inlineStr">
+        <v>0.9959801170018832</v>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1167,7 +1108,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1179,24 +1120,21 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1853224014640688</v>
+        <v>0.9971886554051804</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4470422960134591</v>
+        <v>0.002811344594819546</v>
       </c>
       <c r="G20" t="n">
-        <v>0.367635302522472</v>
+        <v>0.9971886554051804</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4470422960134591</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.07940699349098712</v>
-      </c>
-      <c r="J20" t="inlineStr">
+        <v>0.9943773108103608</v>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1205,11 +1143,11 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1217,24 +1155,21 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2856692057066926</v>
+        <v>0.9973954310744291</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1512760603649108</v>
+        <v>0.002604568925570898</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5630547339283968</v>
+        <v>0.9973954310744291</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5630547339283968</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.2773855282217042</v>
-      </c>
-      <c r="J21" t="inlineStr">
+        <v>0.9947908621488581</v>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1243,7 +1178,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>S50</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1258,21 +1193,18 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5215552480897084</v>
+        <v>0.9969481213522644</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06967082268024603</v>
+        <v>0.003051878647735634</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4087739292300455</v>
+        <v>0.9969481213522644</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5215552480897084</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.112781318859663</v>
-      </c>
-      <c r="J22" t="inlineStr">
+        <v>0.9938962427045288</v>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1281,11 +1213,11 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>S65</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1293,24 +1225,21 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2123293421255624</v>
+        <v>0.9972933191181065</v>
       </c>
       <c r="F23" t="n">
-        <v>0.08696518518845539</v>
+        <v>0.002706680881893532</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7007054726859822</v>
+        <v>0.9972933191181065</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7007054726859822</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.4883761305604198</v>
-      </c>
-      <c r="J23" t="inlineStr">
+        <v>0.994586638236213</v>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1319,11 +1248,11 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S79</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1331,24 +1260,21 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2190017571499815</v>
+        <v>0.9545430703410491</v>
       </c>
       <c r="F24" t="n">
-        <v>0.09973812757749217</v>
+        <v>0.04545692965895083</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6812601152725262</v>
+        <v>0.9545430703410491</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6812601152725262</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.4622583581225446</v>
-      </c>
-      <c r="J24" t="inlineStr">
+        <v>0.9090861406820983</v>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1357,11 +1283,11 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1369,24 +1295,21 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2461070781041891</v>
+        <v>0.9923828587881294</v>
       </c>
       <c r="F25" t="n">
-        <v>0.114428866263508</v>
+        <v>0.007617141211870642</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6394640556323031</v>
+        <v>0.9923828587881294</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6394640556323031</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.393356977528114</v>
-      </c>
-      <c r="J25" t="inlineStr">
+        <v>0.9847657175762587</v>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
@@ -1395,11 +1318,11 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S81</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1407,404 +1330,21 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2822149966032927</v>
+        <v>0.8968747104874916</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1268286668829984</v>
+        <v>0.1031252895125084</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5909563365137088</v>
+        <v>0.8968747104874916</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5909563365137088</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.3087413399104161</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Train</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>S39</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>3</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>3</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.2245662474626217</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.1664406784352645</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.6089930741021139</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.6089930741021139</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.3844268266394922</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Train</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>S50</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>3</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>3</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.1880329073670156</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.1304837393182778</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.6814833533147066</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.6814833533147066</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.4934504459476909</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Train</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>S52</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>2</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>3</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.1688296292738063</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.3339844676546835</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.4971859030715102</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.4971859030715102</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.1632014354168266</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Train</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>S54</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>2</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>3</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.1674606284783993</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.3377787844329196</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.494760587088681</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.494760587088681</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.1569818026557614</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Train</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>S65</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>3</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.270589199656666</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.1409290893652888</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.5884817109780451</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.5884817109780451</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.3178925113213791</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Train</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>S70</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>3</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>3</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.1468979473982679</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.3805588125926484</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.4725432400090837</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.4725432400090837</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.09198442741643531</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Train</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>S72</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>2</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>3</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.1213018035044469</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.2620900867542397</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.6166081097413133</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.6166081097413133</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.3545180229870736</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Train</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>S79</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>3</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>3</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.2209760330111389</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.3181194725097389</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.4609044944791221</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.4609044944791221</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.1427850219693832</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Train</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>3</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.2505613982638615</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.181152964155555</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.5682856375805835</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.5682856375805835</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.317724239316722</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Train</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>S81</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>3</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>3</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.2135711032784456</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.3793723520693767</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.4070565446521777</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.4070565446521777</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.02768419258280097</v>
-      </c>
-      <c r="J36" t="inlineStr">
+        <v>0.7937494209749831</v>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
